--- a/education_forms/048_kindergarten_readiness_survey--education_forms.xlsx
+++ b/education_forms/048_kindergarten_readiness_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -719,8 +719,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'single_parent'}</t>
+          <t>single_parent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Single Parent'}</t>
+          <t>Single Parent</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'married_couple'}</t>
+          <t>married_couple</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Married Couple'}</t>
+          <t>Married Couple</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
